--- a/slots/resources/sample/PlayerLevelPack.xlsx
+++ b/slots/resources/sample/PlayerLevelPack.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="31">
   <si>
     <t>id</t>
   </si>
@@ -64,16 +64,64 @@
     <t>pay</t>
   </si>
   <si>
-    <t>1990000_10000</t>
-  </si>
-  <si>
-    <t>1990000_10000|1022502_2</t>
-  </si>
-  <si>
-    <t>1990000_10000|1022502_2|1010301_2</t>
-  </si>
-  <si>
-    <t>1990000_10000|1022502_2|1010301_2|1010311_3</t>
+    <t>1990000_139000</t>
+  </si>
+  <si>
+    <t>1990000_697000</t>
+  </si>
+  <si>
+    <t>1990000_2946000</t>
+  </si>
+  <si>
+    <t>1990000_12430000|1022502_2</t>
+  </si>
+  <si>
+    <t>1990000_52343000|1022502_2</t>
+  </si>
+  <si>
+    <t>1990000_185000000|1022502_2</t>
+  </si>
+  <si>
+    <t>1990000_651000000|1022502_2</t>
+  </si>
+  <si>
+    <t>1990000_2286000000|1022502_2</t>
+  </si>
+  <si>
+    <t>1990000_6705000000|1022502_2|1010301_2</t>
+  </si>
+  <si>
+    <t>1990000_19600000000|1022502_2|1010301_2</t>
+  </si>
+  <si>
+    <t>1990000_47661000000|1022502_2|1010301_2</t>
+  </si>
+  <si>
+    <t>1990000_115000000000|1022502_2|1010301_2</t>
+  </si>
+  <si>
+    <t>1990000_231000000000|1022502_2|1010301_2</t>
+  </si>
+  <si>
+    <t>1990000_461000000000|1022502_2|1010301_2</t>
+  </si>
+  <si>
+    <t>1990000_757000000000|1022502_2|1010301_2</t>
+  </si>
+  <si>
+    <t>1990000_1232000000000|1022502_2|1010301_2|1010311_3</t>
+  </si>
+  <si>
+    <t>1990000_1641000000000|1022502_2|1010301_2|1010311_3</t>
+  </si>
+  <si>
+    <t>1990000_1778000000000|1022502_2|1010301_2|1010311_3</t>
+  </si>
+  <si>
+    <t>1990000_1897000000000|1022502_2|1010301_2|1010311_3</t>
+  </si>
+  <si>
+    <t>1990000_1982000000000|1022502_2|1010301_2|1010311_3</t>
   </si>
 </sst>
 </file>
@@ -716,7 +764,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -729,17 +777,11 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1073,27 +1115,27 @@
       <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="4" t="s">
         <v>5</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="3" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1107,16 +1149,16 @@
       <c r="C3" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:2">
-      <c r="A4" s="6"/>
-      <c r="B4" s="6"/>
+      <c r="A4" s="5"/>
+      <c r="B4" s="5"/>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="1">
@@ -1125,7 +1167,7 @@
       <c r="B5" s="1">
         <v>10</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D5" s="1">
@@ -1142,8 +1184,8 @@
       <c r="B6" s="1">
         <v>20</v>
       </c>
-      <c r="C6" s="7" t="s">
-        <v>11</v>
+      <c r="C6" s="1" t="s">
+        <v>12</v>
       </c>
       <c r="D6" s="1">
         <v>120</v>
@@ -1159,8 +1201,8 @@
       <c r="B7" s="1">
         <v>30</v>
       </c>
-      <c r="C7" s="7" t="s">
-        <v>11</v>
+      <c r="C7" s="1" t="s">
+        <v>13</v>
       </c>
       <c r="D7" s="1">
         <v>120</v>
@@ -1176,8 +1218,8 @@
       <c r="B8" s="1">
         <v>40</v>
       </c>
-      <c r="C8" s="7" t="s">
-        <v>12</v>
+      <c r="C8" s="1" t="s">
+        <v>14</v>
       </c>
       <c r="D8" s="1">
         <v>120</v>
@@ -1193,8 +1235,8 @@
       <c r="B9" s="1">
         <v>50</v>
       </c>
-      <c r="C9" s="7" t="s">
-        <v>12</v>
+      <c r="C9" s="1" t="s">
+        <v>15</v>
       </c>
       <c r="D9" s="1">
         <v>120</v>
@@ -1210,8 +1252,8 @@
       <c r="B10" s="1">
         <v>60</v>
       </c>
-      <c r="C10" s="7" t="s">
-        <v>12</v>
+      <c r="C10" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="D10" s="1">
         <v>120</v>
@@ -1227,8 +1269,8 @@
       <c r="B11" s="1">
         <v>70</v>
       </c>
-      <c r="C11" s="7" t="s">
-        <v>12</v>
+      <c r="C11" s="1" t="s">
+        <v>17</v>
       </c>
       <c r="D11" s="1">
         <v>120</v>
@@ -1244,8 +1286,8 @@
       <c r="B12" s="1">
         <v>80</v>
       </c>
-      <c r="C12" s="7" t="s">
-        <v>12</v>
+      <c r="C12" s="1" t="s">
+        <v>18</v>
       </c>
       <c r="D12" s="1">
         <v>120</v>
@@ -1261,8 +1303,8 @@
       <c r="B13" s="1">
         <v>90</v>
       </c>
-      <c r="C13" s="7" t="s">
-        <v>13</v>
+      <c r="C13" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="D13" s="1">
         <v>120</v>
@@ -1278,8 +1320,8 @@
       <c r="B14" s="1">
         <v>100</v>
       </c>
-      <c r="C14" s="7" t="s">
-        <v>13</v>
+      <c r="C14" s="1" t="s">
+        <v>20</v>
       </c>
       <c r="D14" s="1">
         <v>120</v>
@@ -1295,8 +1337,8 @@
       <c r="B15" s="1">
         <v>110</v>
       </c>
-      <c r="C15" s="7" t="s">
-        <v>13</v>
+      <c r="C15" s="1" t="s">
+        <v>21</v>
       </c>
       <c r="D15" s="1">
         <v>120</v>
@@ -1312,8 +1354,8 @@
       <c r="B16" s="1">
         <v>120</v>
       </c>
-      <c r="C16" s="7" t="s">
-        <v>13</v>
+      <c r="C16" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="D16" s="1">
         <v>120</v>
@@ -1329,8 +1371,8 @@
       <c r="B17" s="1">
         <v>130</v>
       </c>
-      <c r="C17" s="7" t="s">
-        <v>13</v>
+      <c r="C17" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="D17" s="1">
         <v>120</v>
@@ -1346,8 +1388,8 @@
       <c r="B18" s="1">
         <v>140</v>
       </c>
-      <c r="C18" s="7" t="s">
-        <v>13</v>
+      <c r="C18" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="D18" s="1">
         <v>120</v>
@@ -1363,8 +1405,8 @@
       <c r="B19" s="1">
         <v>150</v>
       </c>
-      <c r="C19" s="7" t="s">
-        <v>13</v>
+      <c r="C19" s="1" t="s">
+        <v>25</v>
       </c>
       <c r="D19" s="1">
         <v>120</v>
@@ -1380,8 +1422,8 @@
       <c r="B20" s="1">
         <v>160</v>
       </c>
-      <c r="C20" s="7" t="s">
-        <v>14</v>
+      <c r="C20" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="D20" s="1">
         <v>120</v>
@@ -1397,8 +1439,8 @@
       <c r="B21" s="1">
         <v>170</v>
       </c>
-      <c r="C21" s="7" t="s">
-        <v>14</v>
+      <c r="C21" s="1" t="s">
+        <v>27</v>
       </c>
       <c r="D21" s="1">
         <v>120</v>
@@ -1414,8 +1456,8 @@
       <c r="B22" s="1">
         <v>180</v>
       </c>
-      <c r="C22" s="7" t="s">
-        <v>14</v>
+      <c r="C22" s="1" t="s">
+        <v>28</v>
       </c>
       <c r="D22" s="1">
         <v>120</v>
@@ -1431,8 +1473,8 @@
       <c r="B23" s="1">
         <v>190</v>
       </c>
-      <c r="C23" s="7" t="s">
-        <v>14</v>
+      <c r="C23" s="1" t="s">
+        <v>29</v>
       </c>
       <c r="D23" s="1">
         <v>120</v>
@@ -1448,8 +1490,8 @@
       <c r="B24" s="1">
         <v>200</v>
       </c>
-      <c r="C24" s="7" t="s">
-        <v>14</v>
+      <c r="C24" s="1" t="s">
+        <v>30</v>
       </c>
       <c r="D24" s="1">
         <v>120</v>

--- a/slots/resources/sample/PlayerLevelPack.xlsx
+++ b/slots/resources/sample/PlayerLevelPack.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29231"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\java\gamedoc\游戏配置表\common\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FB1AA7D-F4D3-4263-9E53-FFBDF73AF583}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PlayerLevelPack" sheetId="1" r:id="rId1"/>
@@ -29,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="32">
   <si>
     <t>id</t>
   </si>
@@ -122,19 +128,17 @@
   </si>
   <si>
     <t>1990000_1982000000000|1022502_2|1010301_2|1010311_3</t>
+  </si>
+  <si>
+    <t>BigDecimal</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="21">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -149,151 +153,27 @@
       <charset val="134"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
+      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <sz val="9"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -302,198 +182,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -516,255 +210,13 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -777,68 +229,27 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1088,24 +499,24 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E24"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="12.35" style="1" customWidth="1"/>
-    <col min="2" max="2" width="15.4416666666667" style="1" customWidth="1"/>
-    <col min="3" max="3" width="50.2916666666667" style="1" customWidth="1"/>
+    <col min="1" max="1" width="12.375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5" style="1" customWidth="1"/>
+    <col min="3" max="3" width="50.25" style="1" customWidth="1"/>
     <col min="4" max="4" width="14.375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="14.1166666666667" style="1" customWidth="1"/>
+    <col min="5" max="5" width="14.125" style="1" customWidth="1"/>
     <col min="6" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1122,7 +533,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A2" s="4" t="s">
         <v>5</v>
       </c>
@@ -1135,11 +546,11 @@
       <c r="D2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
+      <c r="E2" s="6" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
@@ -1156,11 +567,11 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A4" s="5"/>
       <c r="B4" s="5"/>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -1177,7 +588,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A6" s="1">
         <v>2</v>
       </c>
@@ -1194,7 +605,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A7" s="1">
         <v>3</v>
       </c>
@@ -1211,7 +622,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A8" s="1">
         <v>4</v>
       </c>
@@ -1228,7 +639,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A9" s="1">
         <v>5</v>
       </c>
@@ -1245,7 +656,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A10" s="1">
         <v>6</v>
       </c>
@@ -1262,7 +673,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A11" s="1">
         <v>7</v>
       </c>
@@ -1279,7 +690,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A12" s="1">
         <v>8</v>
       </c>
@@ -1296,7 +707,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A13" s="1">
         <v>9</v>
       </c>
@@ -1313,7 +724,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A14" s="1">
         <v>10</v>
       </c>
@@ -1330,7 +741,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A15" s="1">
         <v>11</v>
       </c>
@@ -1347,7 +758,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A16" s="1">
         <v>12</v>
       </c>
@@ -1364,7 +775,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A17" s="1">
         <v>13</v>
       </c>
@@ -1381,7 +792,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A18" s="1">
         <v>14</v>
       </c>
@@ -1398,7 +809,7 @@
         <v>2999</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A19" s="1">
         <v>15</v>
       </c>
@@ -1415,7 +826,7 @@
         <v>2999</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A20" s="1">
         <v>16</v>
       </c>
@@ -1432,7 +843,7 @@
         <v>2999</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A21" s="1">
         <v>17</v>
       </c>
@@ -1449,7 +860,7 @@
         <v>2999</v>
       </c>
     </row>
-    <row r="22" spans="1:5">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A22" s="1">
         <v>18</v>
       </c>
@@ -1466,7 +877,7 @@
         <v>9999</v>
       </c>
     </row>
-    <row r="23" spans="1:5">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A23" s="1">
         <v>19</v>
       </c>
@@ -1483,7 +894,7 @@
         <v>9999</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A24" s="1">
         <v>20</v>
       </c>
@@ -1501,32 +912,30 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData/>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData/>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/slots/resources/sample/PlayerLevelPack.xlsx
+++ b/slots/resources/sample/PlayerLevelPack.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29231"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\java\gamedoc\游戏配置表\common\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FB1AA7D-F4D3-4263-9E53-FFBDF73AF583}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="PlayerLevelPack" sheetId="1" r:id="rId1"/>
@@ -58,6 +52,9 @@
     <t>map&lt;int{_}long&gt;{|}</t>
   </si>
   <si>
+    <t>BigDecimal</t>
+  </si>
+  <si>
     <t>playerlevel</t>
   </si>
   <si>
@@ -128,17 +125,19 @@
   </si>
   <si>
     <t>1990000_1982000000000|1022502_2|1010301_2|1010311_3</t>
-  </si>
-  <si>
-    <t>BigDecimal</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -153,27 +152,151 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="微软雅黑"/>
-      <family val="2"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -182,12 +305,204 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
+        <fgColor theme="5" tint="0.6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6C6AC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -210,9 +525,251 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -229,27 +786,71 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -499,24 +1100,24 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:E24"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="12.375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="15.5" style="1" customWidth="1"/>
-    <col min="3" max="3" width="50.25" style="1" customWidth="1"/>
+    <col min="1" max="1" width="12.35" style="1" customWidth="1"/>
+    <col min="2" max="2" width="15.4416666666667" style="1" customWidth="1"/>
+    <col min="3" max="3" width="50.2916666666667" style="1" customWidth="1"/>
     <col min="4" max="4" width="14.375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="14.125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="14.1166666666667" style="1" customWidth="1"/>
     <col min="6" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:5">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -533,7 +1134,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:5">
       <c r="A2" s="4" t="s">
         <v>5</v>
       </c>
@@ -546,32 +1147,32 @@
       <c r="D2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="6" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="E2" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A4" s="5"/>
-      <c r="B4" s="5"/>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.15">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" s="6"/>
+      <c r="B4" s="6"/>
+    </row>
+    <row r="5" spans="1:5">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -579,16 +1180,16 @@
         <v>10</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D5" s="1">
         <v>120</v>
       </c>
       <c r="E5" s="1">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.15">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
       <c r="A6" s="1">
         <v>2</v>
       </c>
@@ -596,16 +1197,16 @@
         <v>20</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D6" s="1">
         <v>120</v>
       </c>
       <c r="E6" s="1">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.15">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
       <c r="A7" s="1">
         <v>3</v>
       </c>
@@ -613,16 +1214,16 @@
         <v>30</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D7" s="1">
         <v>120</v>
       </c>
       <c r="E7" s="1">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.15">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
       <c r="A8" s="1">
         <v>4</v>
       </c>
@@ -630,16 +1231,16 @@
         <v>40</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D8" s="1">
         <v>120</v>
       </c>
       <c r="E8" s="1">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.15">
+        <v>4.99</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
       <c r="A9" s="1">
         <v>5</v>
       </c>
@@ -647,16 +1248,16 @@
         <v>50</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D9" s="1">
         <v>120</v>
       </c>
       <c r="E9" s="1">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.15">
+        <v>4.99</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
       <c r="A10" s="1">
         <v>6</v>
       </c>
@@ -664,16 +1265,16 @@
         <v>60</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D10" s="1">
         <v>120</v>
       </c>
       <c r="E10" s="1">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.15">
+        <v>4.99</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
       <c r="A11" s="1">
         <v>7</v>
       </c>
@@ -681,16 +1282,16 @@
         <v>70</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D11" s="1">
         <v>120</v>
       </c>
       <c r="E11" s="1">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.15">
+        <v>4.99</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
       <c r="A12" s="1">
         <v>8</v>
       </c>
@@ -698,16 +1299,16 @@
         <v>80</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D12" s="1">
         <v>120</v>
       </c>
       <c r="E12" s="1">
-        <v>999</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.15">
+        <v>9.99</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
       <c r="A13" s="1">
         <v>9</v>
       </c>
@@ -715,16 +1316,16 @@
         <v>90</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D13" s="1">
         <v>120</v>
       </c>
       <c r="E13" s="1">
-        <v>999</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.15">
+        <v>9.99</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
       <c r="A14" s="1">
         <v>10</v>
       </c>
@@ -732,16 +1333,16 @@
         <v>100</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D14" s="1">
         <v>120</v>
       </c>
       <c r="E14" s="1">
-        <v>999</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.15">
+        <v>9.99</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
       <c r="A15" s="1">
         <v>11</v>
       </c>
@@ -749,16 +1350,16 @@
         <v>110</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D15" s="1">
         <v>120</v>
       </c>
       <c r="E15" s="1">
-        <v>999</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.15">
+        <v>9.99</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
       <c r="A16" s="1">
         <v>12</v>
       </c>
@@ -766,16 +1367,16 @@
         <v>120</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D16" s="1">
         <v>120</v>
       </c>
       <c r="E16" s="1">
-        <v>999</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.15">
+        <v>9.99</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
       <c r="A17" s="1">
         <v>13</v>
       </c>
@@ -783,16 +1384,16 @@
         <v>130</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D17" s="1">
         <v>120</v>
       </c>
       <c r="E17" s="1">
-        <v>999</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.15">
+        <v>9.99</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
       <c r="A18" s="1">
         <v>14</v>
       </c>
@@ -800,16 +1401,16 @@
         <v>140</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D18" s="1">
         <v>120</v>
       </c>
       <c r="E18" s="1">
-        <v>2999</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.15">
+        <v>29.99</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
       <c r="A19" s="1">
         <v>15</v>
       </c>
@@ -817,16 +1418,16 @@
         <v>150</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D19" s="1">
         <v>120</v>
       </c>
       <c r="E19" s="1">
-        <v>2999</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.15">
+        <v>29.99</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
       <c r="A20" s="1">
         <v>16</v>
       </c>
@@ -834,16 +1435,16 @@
         <v>160</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D20" s="1">
         <v>120</v>
       </c>
       <c r="E20" s="1">
-        <v>2999</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.15">
+        <v>29.99</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
       <c r="A21" s="1">
         <v>17</v>
       </c>
@@ -851,16 +1452,16 @@
         <v>170</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D21" s="1">
         <v>120</v>
       </c>
       <c r="E21" s="1">
-        <v>2999</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.15">
+        <v>29.99</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
       <c r="A22" s="1">
         <v>18</v>
       </c>
@@ -868,16 +1469,16 @@
         <v>180</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D22" s="1">
         <v>120</v>
       </c>
       <c r="E22" s="1">
-        <v>9999</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.15">
+        <v>99.99</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
       <c r="A23" s="1">
         <v>19</v>
       </c>
@@ -885,16 +1486,16 @@
         <v>190</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D23" s="1">
         <v>120</v>
       </c>
       <c r="E23" s="1">
-        <v>9999</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.15">
+        <v>99.99</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
       <c r="A24" s="1">
         <v>20</v>
       </c>
@@ -902,40 +1503,42 @@
         <v>200</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D24" s="1">
         <v>120</v>
       </c>
       <c r="E24" s="1">
-        <v>9999</v>
+        <v>99.99</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData/>
-  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData/>
-  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/slots/resources/sample/PlayerLevelPack.xlsx
+++ b/slots/resources/sample/PlayerLevelPack.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="32">
   <si>
     <t>id</t>
   </si>
@@ -50,6 +50,9 @@
   </si>
   <si>
     <t>map&lt;int{_}long&gt;{|}</t>
+  </si>
+  <si>
+    <t>BigDecimal</t>
   </si>
   <si>
     <t>playerlevel</t>
@@ -293,7 +296,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -303,6 +306,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6C6AC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -640,7 +649,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -664,16 +673,16 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -682,89 +691,89 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -778,6 +787,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1135,8 +1147,8 @@
       <c r="D2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="3" t="s">
-        <v>5</v>
+      <c r="E2" s="5" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1144,21 +1156,21 @@
         <v>0</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:2">
-      <c r="A4" s="5"/>
-      <c r="B4" s="5"/>
+      <c r="A4" s="6"/>
+      <c r="B4" s="6"/>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="1">
@@ -1168,13 +1180,13 @@
         <v>10</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D5" s="1">
         <v>120</v>
       </c>
       <c r="E5" s="1">
-        <v>99</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -1185,13 +1197,13 @@
         <v>20</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D6" s="1">
         <v>120</v>
       </c>
       <c r="E6" s="1">
-        <v>99</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -1202,13 +1214,13 @@
         <v>30</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D7" s="1">
         <v>120</v>
       </c>
       <c r="E7" s="1">
-        <v>99</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -1219,13 +1231,13 @@
         <v>40</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D8" s="1">
         <v>120</v>
       </c>
       <c r="E8" s="1">
-        <v>499</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -1236,13 +1248,13 @@
         <v>50</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D9" s="1">
         <v>120</v>
       </c>
       <c r="E9" s="1">
-        <v>499</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -1253,13 +1265,13 @@
         <v>60</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D10" s="1">
         <v>120</v>
       </c>
       <c r="E10" s="1">
-        <v>499</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -1270,13 +1282,13 @@
         <v>70</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D11" s="1">
         <v>120</v>
       </c>
       <c r="E11" s="1">
-        <v>499</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -1287,13 +1299,13 @@
         <v>80</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D12" s="1">
         <v>120</v>
       </c>
       <c r="E12" s="1">
-        <v>999</v>
+        <v>9.99</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -1304,13 +1316,13 @@
         <v>90</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D13" s="1">
         <v>120</v>
       </c>
       <c r="E13" s="1">
-        <v>999</v>
+        <v>9.99</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -1321,13 +1333,13 @@
         <v>100</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D14" s="1">
         <v>120</v>
       </c>
       <c r="E14" s="1">
-        <v>999</v>
+        <v>9.99</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -1338,13 +1350,13 @@
         <v>110</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D15" s="1">
         <v>120</v>
       </c>
       <c r="E15" s="1">
-        <v>999</v>
+        <v>9.99</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -1355,13 +1367,13 @@
         <v>120</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D16" s="1">
         <v>120</v>
       </c>
       <c r="E16" s="1">
-        <v>999</v>
+        <v>9.99</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1372,13 +1384,13 @@
         <v>130</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D17" s="1">
         <v>120</v>
       </c>
       <c r="E17" s="1">
-        <v>999</v>
+        <v>9.99</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1389,13 +1401,13 @@
         <v>140</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D18" s="1">
         <v>120</v>
       </c>
       <c r="E18" s="1">
-        <v>2999</v>
+        <v>29.99</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1406,13 +1418,13 @@
         <v>150</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D19" s="1">
         <v>120</v>
       </c>
       <c r="E19" s="1">
-        <v>2999</v>
+        <v>29.99</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1423,13 +1435,13 @@
         <v>160</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D20" s="1">
         <v>120</v>
       </c>
       <c r="E20" s="1">
-        <v>2999</v>
+        <v>29.99</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1440,13 +1452,13 @@
         <v>170</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D21" s="1">
         <v>120</v>
       </c>
       <c r="E21" s="1">
-        <v>2999</v>
+        <v>29.99</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -1457,13 +1469,13 @@
         <v>180</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D22" s="1">
         <v>120</v>
       </c>
       <c r="E22" s="1">
-        <v>9999</v>
+        <v>99.99</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1474,13 +1486,13 @@
         <v>190</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D23" s="1">
         <v>120</v>
       </c>
       <c r="E23" s="1">
-        <v>9999</v>
+        <v>99.99</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -1491,13 +1503,13 @@
         <v>200</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D24" s="1">
         <v>120</v>
       </c>
       <c r="E24" s="1">
-        <v>9999</v>
+        <v>99.99</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/PlayerLevelPack.xlsx
+++ b/slots/resources/sample/PlayerLevelPack.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27735" windowHeight="12270"/>
   </bookViews>
   <sheets>
     <sheet name="PlayerLevelPack" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="31">
   <si>
     <t>id</t>
   </si>
@@ -67,64 +67,61 @@
     <t>pay</t>
   </si>
   <si>
-    <t>1990000_139000</t>
-  </si>
-  <si>
-    <t>1990000_697000</t>
-  </si>
-  <si>
-    <t>1990000_2946000</t>
-  </si>
-  <si>
-    <t>1990000_12430000|1022502_2</t>
-  </si>
-  <si>
-    <t>1990000_52343000|1022502_2</t>
-  </si>
-  <si>
-    <t>1990000_185000000|1022502_2</t>
-  </si>
-  <si>
-    <t>1990000_651000000|1022502_2</t>
-  </si>
-  <si>
-    <t>1990000_2286000000|1022502_2</t>
-  </si>
-  <si>
-    <t>1990000_6705000000|1022502_2|1010301_2</t>
-  </si>
-  <si>
-    <t>1990000_19600000000|1022502_2|1010301_2</t>
-  </si>
-  <si>
-    <t>1990000_47661000000|1022502_2|1010301_2</t>
-  </si>
-  <si>
-    <t>1990000_115000000000|1022502_2|1010301_2</t>
-  </si>
-  <si>
-    <t>1990000_231000000000|1022502_2|1010301_2</t>
-  </si>
-  <si>
-    <t>1990000_461000000000|1022502_2|1010301_2</t>
-  </si>
-  <si>
-    <t>1990000_757000000000|1022502_2|1010301_2</t>
-  </si>
-  <si>
-    <t>1990000_1232000000000|1022502_2|1010301_2|1010311_3</t>
-  </si>
-  <si>
-    <t>1990000_1641000000000|1022502_2|1010301_2|1010311_3</t>
-  </si>
-  <si>
-    <t>1990000_1778000000000|1022502_2|1010301_2|1010311_3</t>
-  </si>
-  <si>
-    <t>1990000_1897000000000|1022502_2|1010301_2|1010311_3</t>
-  </si>
-  <si>
-    <t>1990000_1982000000000|1022502_2|1010301_2|1010311_3</t>
+    <t>1990000_2475000</t>
+  </si>
+  <si>
+    <t>1990000_4975000</t>
+  </si>
+  <si>
+    <t>1990000_7277000|1022502_2</t>
+  </si>
+  <si>
+    <t>1990000_14777000|1022502_2</t>
+  </si>
+  <si>
+    <t>1990000_20576000|1022502_2</t>
+  </si>
+  <si>
+    <t>1990000_26775000|1022502_2</t>
+  </si>
+  <si>
+    <t>1990000_41477000|1022502_5</t>
+  </si>
+  <si>
+    <t>1990000_57277000|1022502_5|1010301_1</t>
+  </si>
+  <si>
+    <t>1990000_74077000|1022502_5|1010301_2</t>
+  </si>
+  <si>
+    <t>1990000_157980000|1022502_10|1010302_2</t>
+  </si>
+  <si>
+    <t>1990000_167978000|1022502_10|1010302_2</t>
+  </si>
+  <si>
+    <t>1990000_177976000|1022502_10|1010302_2</t>
+  </si>
+  <si>
+    <t>1990000_187974000|1022502_10|1010302_2</t>
+  </si>
+  <si>
+    <t>1990000_197972000|1022502_10|1010302_2</t>
+  </si>
+  <si>
+    <t>1990000_414980000|1022502_20|1010303_2</t>
+  </si>
+  <si>
+    <t>1990000_434978000|1022502_20|1010303_2</t>
+  </si>
+  <si>
+    <t>1990000_454976000|1022502_20|1010303_2</t>
+  </si>
+  <si>
+    <t>1990000_474974000|1022502_20|1010303_2</t>
+  </si>
+  <si>
+    <t>1990000_494972000|1022502_20|1010303_2</t>
   </si>
 </sst>
 </file>
@@ -1197,7 +1194,7 @@
         <v>20</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D6" s="1">
         <v>120</v>
@@ -1214,13 +1211,13 @@
         <v>30</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D7" s="1">
         <v>120</v>
       </c>
       <c r="E7" s="1">
-        <v>0.99</v>
+        <v>1.99</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -1231,13 +1228,13 @@
         <v>40</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D8" s="1">
         <v>120</v>
       </c>
       <c r="E8" s="1">
-        <v>4.99</v>
+        <v>2.99</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -1248,13 +1245,13 @@
         <v>50</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D9" s="1">
         <v>120</v>
       </c>
       <c r="E9" s="1">
-        <v>4.99</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -1265,13 +1262,13 @@
         <v>60</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D10" s="1">
         <v>120</v>
       </c>
       <c r="E10" s="1">
-        <v>4.99</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -1282,13 +1279,13 @@
         <v>70</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D11" s="1">
         <v>120</v>
       </c>
       <c r="E11" s="1">
-        <v>4.99</v>
+        <v>9.99</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -1299,13 +1296,13 @@
         <v>80</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D12" s="1">
         <v>120</v>
       </c>
       <c r="E12" s="1">
-        <v>9.99</v>
+        <v>14.99</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -1316,13 +1313,13 @@
         <v>90</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D13" s="1">
         <v>120</v>
       </c>
       <c r="E13" s="1">
-        <v>9.99</v>
+        <v>19.99</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -1333,13 +1330,13 @@
         <v>100</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D14" s="1">
         <v>120</v>
       </c>
       <c r="E14" s="1">
-        <v>9.99</v>
+        <v>24.99</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -1350,13 +1347,13 @@
         <v>110</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D15" s="1">
         <v>120</v>
       </c>
       <c r="E15" s="1">
-        <v>9.99</v>
+        <v>49.99</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -1367,13 +1364,13 @@
         <v>120</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D16" s="1">
         <v>120</v>
       </c>
       <c r="E16" s="1">
-        <v>9.99</v>
+        <v>49.99</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1384,13 +1381,13 @@
         <v>130</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D17" s="1">
         <v>120</v>
       </c>
       <c r="E17" s="1">
-        <v>9.99</v>
+        <v>49.99</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1401,13 +1398,13 @@
         <v>140</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D18" s="1">
         <v>120</v>
       </c>
       <c r="E18" s="1">
-        <v>29.99</v>
+        <v>49.99</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1418,13 +1415,13 @@
         <v>150</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D19" s="1">
         <v>120</v>
       </c>
       <c r="E19" s="1">
-        <v>29.99</v>
+        <v>49.99</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1435,13 +1432,13 @@
         <v>160</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D20" s="1">
         <v>120</v>
       </c>
       <c r="E20" s="1">
-        <v>29.99</v>
+        <v>99.99</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1452,13 +1449,13 @@
         <v>170</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D21" s="1">
         <v>120</v>
       </c>
       <c r="E21" s="1">
-        <v>29.99</v>
+        <v>99.99</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -1469,7 +1466,7 @@
         <v>180</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D22" s="1">
         <v>120</v>
@@ -1486,7 +1483,7 @@
         <v>190</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D23" s="1">
         <v>120</v>
@@ -1503,7 +1500,7 @@
         <v>200</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D24" s="1">
         <v>120</v>

--- a/slots/resources/sample/PlayerLevelPack.xlsx
+++ b/slots/resources/sample/PlayerLevelPack.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29231"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\java\gamedoc\游戏配置表\common\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4A6CC1C-0EE6-4235-ACA7-14CC76D6BA84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="27735" windowHeight="12270"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PlayerLevelPack" sheetId="1" r:id="rId1"/>
@@ -29,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="54">
   <si>
     <t>id</t>
   </si>
@@ -122,19 +128,82 @@
   </si>
   <si>
     <t>1990000_494972000|1022502_20|1010303_2</t>
+  </si>
+  <si>
+    <t>渠道商品ID</t>
+  </si>
+  <si>
+    <t>map&lt;int{_}String&gt;{|}</t>
+  </si>
+  <si>
+    <t>channelCommodity</t>
+  </si>
+  <si>
+    <t>1_1|2_2</t>
+  </si>
+  <si>
+    <t>1_1|2_3</t>
+  </si>
+  <si>
+    <t>1_1|2_4</t>
+  </si>
+  <si>
+    <t>1_1|2_5</t>
+  </si>
+  <si>
+    <t>1_1|2_6</t>
+  </si>
+  <si>
+    <t>1_1|2_7</t>
+  </si>
+  <si>
+    <t>1_1|2_8</t>
+  </si>
+  <si>
+    <t>1_1|2_9</t>
+  </si>
+  <si>
+    <t>1_1|2_10</t>
+  </si>
+  <si>
+    <t>1_1|2_11</t>
+  </si>
+  <si>
+    <t>1_1|2_12</t>
+  </si>
+  <si>
+    <t>1_1|2_13</t>
+  </si>
+  <si>
+    <t>1_1|2_14</t>
+  </si>
+  <si>
+    <t>1_1|2_15</t>
+  </si>
+  <si>
+    <t>1_1|2_16</t>
+  </si>
+  <si>
+    <t>1_1|2_17</t>
+  </si>
+  <si>
+    <t>1_1|2_18</t>
+  </si>
+  <si>
+    <t>1_1|2_19</t>
+  </si>
+  <si>
+    <t>1_1|2_20</t>
+  </si>
+  <si>
+    <t>1_1|2_21</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="21">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -149,151 +218,13 @@
       <charset val="134"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
+      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="35">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -302,7 +233,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.6"/>
+        <fgColor theme="5" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -312,194 +243,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="10">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -522,251 +267,9 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -783,71 +286,27 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1097,24 +556,25 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:E24"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:F24"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="12.35" style="1" customWidth="1"/>
-    <col min="2" max="2" width="15.4416666666667" style="1" customWidth="1"/>
-    <col min="3" max="3" width="50.2916666666667" style="1" customWidth="1"/>
+    <col min="1" max="1" width="12.375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5" style="1" customWidth="1"/>
+    <col min="3" max="3" width="50.25" style="1" customWidth="1"/>
     <col min="4" max="4" width="14.375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="14.1166666666667" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9" style="1"/>
+    <col min="5" max="5" width="14.125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="21.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1130,8 +590,11 @@
       <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5">
+      <c r="F1" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A2" s="4" t="s">
         <v>5</v>
       </c>
@@ -1147,8 +610,11 @@
       <c r="E2" s="5" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="3" spans="1:5">
+      <c r="F2" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
@@ -1164,12 +630,15 @@
       <c r="E3" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="4" spans="1:2">
+      <c r="F3" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A4" s="6"/>
       <c r="B4" s="6"/>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -1185,8 +654,11 @@
       <c r="E5" s="1">
         <v>0.99</v>
       </c>
-    </row>
-    <row r="6" spans="1:5">
+      <c r="F5" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A6" s="1">
         <v>2</v>
       </c>
@@ -1202,8 +674,11 @@
       <c r="E6" s="1">
         <v>0.99</v>
       </c>
-    </row>
-    <row r="7" spans="1:5">
+      <c r="F6" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A7" s="1">
         <v>3</v>
       </c>
@@ -1219,8 +694,11 @@
       <c r="E7" s="1">
         <v>1.99</v>
       </c>
-    </row>
-    <row r="8" spans="1:5">
+      <c r="F7" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A8" s="1">
         <v>4</v>
       </c>
@@ -1236,8 +714,11 @@
       <c r="E8" s="1">
         <v>2.99</v>
       </c>
-    </row>
-    <row r="9" spans="1:5">
+      <c r="F8" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A9" s="1">
         <v>5</v>
       </c>
@@ -1253,8 +734,11 @@
       <c r="E9" s="1">
         <v>5.99</v>
       </c>
-    </row>
-    <row r="10" spans="1:5">
+      <c r="F9" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A10" s="1">
         <v>6</v>
       </c>
@@ -1270,8 +754,11 @@
       <c r="E10" s="1">
         <v>7.99</v>
       </c>
-    </row>
-    <row r="11" spans="1:5">
+      <c r="F10" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A11" s="1">
         <v>7</v>
       </c>
@@ -1287,8 +774,11 @@
       <c r="E11" s="1">
         <v>9.99</v>
       </c>
-    </row>
-    <row r="12" spans="1:5">
+      <c r="F11" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A12" s="1">
         <v>8</v>
       </c>
@@ -1304,8 +794,11 @@
       <c r="E12" s="1">
         <v>14.99</v>
       </c>
-    </row>
-    <row r="13" spans="1:5">
+      <c r="F12" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A13" s="1">
         <v>9</v>
       </c>
@@ -1319,10 +812,13 @@
         <v>120</v>
       </c>
       <c r="E13" s="1">
-        <v>19.99</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
+        <v>19.989999999999998</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A14" s="1">
         <v>10</v>
       </c>
@@ -1338,8 +834,11 @@
       <c r="E14" s="1">
         <v>24.99</v>
       </c>
-    </row>
-    <row r="15" spans="1:5">
+      <c r="F14" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A15" s="1">
         <v>11</v>
       </c>
@@ -1355,8 +854,11 @@
       <c r="E15" s="1">
         <v>49.99</v>
       </c>
-    </row>
-    <row r="16" spans="1:5">
+      <c r="F15" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A16" s="1">
         <v>12</v>
       </c>
@@ -1372,8 +874,11 @@
       <c r="E16" s="1">
         <v>49.99</v>
       </c>
-    </row>
-    <row r="17" spans="1:5">
+      <c r="F16" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A17" s="1">
         <v>13</v>
       </c>
@@ -1389,8 +894,11 @@
       <c r="E17" s="1">
         <v>49.99</v>
       </c>
-    </row>
-    <row r="18" spans="1:5">
+      <c r="F17" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A18" s="1">
         <v>14</v>
       </c>
@@ -1406,8 +914,11 @@
       <c r="E18" s="1">
         <v>49.99</v>
       </c>
-    </row>
-    <row r="19" spans="1:5">
+      <c r="F18" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A19" s="1">
         <v>15</v>
       </c>
@@ -1423,8 +934,11 @@
       <c r="E19" s="1">
         <v>49.99</v>
       </c>
-    </row>
-    <row r="20" spans="1:5">
+      <c r="F19" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A20" s="1">
         <v>16</v>
       </c>
@@ -1440,8 +954,11 @@
       <c r="E20" s="1">
         <v>99.99</v>
       </c>
-    </row>
-    <row r="21" spans="1:5">
+      <c r="F20" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A21" s="1">
         <v>17</v>
       </c>
@@ -1457,8 +974,11 @@
       <c r="E21" s="1">
         <v>99.99</v>
       </c>
-    </row>
-    <row r="22" spans="1:5">
+      <c r="F21" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A22" s="1">
         <v>18</v>
       </c>
@@ -1474,8 +994,11 @@
       <c r="E22" s="1">
         <v>99.99</v>
       </c>
-    </row>
-    <row r="23" spans="1:5">
+      <c r="F22" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A23" s="1">
         <v>19</v>
       </c>
@@ -1491,8 +1014,11 @@
       <c r="E23" s="1">
         <v>99.99</v>
       </c>
-    </row>
-    <row r="24" spans="1:5">
+      <c r="F23" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A24" s="1">
         <v>20</v>
       </c>
@@ -1508,34 +1034,35 @@
       <c r="E24" s="1">
         <v>99.99</v>
       </c>
+      <c r="F24" s="1" t="s">
+        <v>53</v>
+      </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData/>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData/>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/slots/resources/sample/PlayerLevelPack.xlsx
+++ b/slots/resources/sample/PlayerLevelPack.xlsx
@@ -28,8 +28,41 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Administrator</author>
+  </authors>
+  <commentList>
+    <comment ref="F1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+1_1|2_2 ： 渠道1id_对应的商品id|渠道2id_对应的商品id
+注：1 =  google渠道ID；2 = apple 渠道ID</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="45">
   <si>
     <t>id</t>
   </si>
@@ -46,6 +79,9 @@
     <t>购买金额</t>
   </si>
   <si>
+    <t>渠道商品ID</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
@@ -55,6 +91,9 @@
     <t>BigDecimal</t>
   </si>
   <si>
+    <t>map&lt;int{_}String&gt;{|}</t>
+  </si>
+  <si>
     <t>playerlevel</t>
   </si>
   <si>
@@ -67,64 +106,97 @@
     <t>pay</t>
   </si>
   <si>
-    <t>1990000_139000</t>
-  </si>
-  <si>
-    <t>1990000_697000</t>
-  </si>
-  <si>
-    <t>1990000_2946000</t>
-  </si>
-  <si>
-    <t>1990000_12430000|1022502_2</t>
-  </si>
-  <si>
-    <t>1990000_52343000|1022502_2</t>
-  </si>
-  <si>
-    <t>1990000_185000000|1022502_2</t>
-  </si>
-  <si>
-    <t>1990000_651000000|1022502_2</t>
-  </si>
-  <si>
-    <t>1990000_2286000000|1022502_2</t>
-  </si>
-  <si>
-    <t>1990000_6705000000|1022502_2|1010301_2</t>
-  </si>
-  <si>
-    <t>1990000_19600000000|1022502_2|1010301_2</t>
-  </si>
-  <si>
-    <t>1990000_47661000000|1022502_2|1010301_2</t>
-  </si>
-  <si>
-    <t>1990000_115000000000|1022502_2|1010301_2</t>
-  </si>
-  <si>
-    <t>1990000_231000000000|1022502_2|1010301_2</t>
-  </si>
-  <si>
-    <t>1990000_461000000000|1022502_2|1010301_2</t>
-  </si>
-  <si>
-    <t>1990000_757000000000|1022502_2|1010301_2</t>
-  </si>
-  <si>
-    <t>1990000_1232000000000|1022502_2|1010301_2|1010311_3</t>
-  </si>
-  <si>
-    <t>1990000_1641000000000|1022502_2|1010301_2|1010311_3</t>
-  </si>
-  <si>
-    <t>1990000_1778000000000|1022502_2|1010301_2|1010311_3</t>
-  </si>
-  <si>
-    <t>1990000_1897000000000|1022502_2|1010301_2|1010311_3</t>
-  </si>
-  <si>
-    <t>1990000_1982000000000|1022502_2|1010301_2|1010311_3</t>
+    <t>channelCommodity</t>
+  </si>
+  <si>
+    <t>1990000_2475000</t>
+  </si>
+  <si>
+    <t>1_google99|2_ios99</t>
+  </si>
+  <si>
+    <t>1990000_4975000</t>
+  </si>
+  <si>
+    <t>1_google199|2_ios199</t>
+  </si>
+  <si>
+    <t>1990000_7277000|1022502_2</t>
+  </si>
+  <si>
+    <t>1_googl299|2_ios299</t>
+  </si>
+  <si>
+    <t>1990000_14777000|1022502_2</t>
+  </si>
+  <si>
+    <t>1_google599|2_ios599</t>
+  </si>
+  <si>
+    <t>1990000_20576000|1022502_2</t>
+  </si>
+  <si>
+    <t>1_google799|2_ios799</t>
+  </si>
+  <si>
+    <t>1990000_26775000|1022502_2</t>
+  </si>
+  <si>
+    <t>1_google999|2_ios999</t>
+  </si>
+  <si>
+    <t>1990000_41477000|1022502_5</t>
+  </si>
+  <si>
+    <t>1_google1499|2_ios1499</t>
+  </si>
+  <si>
+    <t>1990000_57277000|1022502_5|1010301_1</t>
+  </si>
+  <si>
+    <t>1_google1999|2_ios1999</t>
+  </si>
+  <si>
+    <t>1990000_74077000|1022502_5|1010301_2</t>
+  </si>
+  <si>
+    <t>1_google2499|2_ios2499</t>
+  </si>
+  <si>
+    <t>1990000_157980000|1022502_10|1010302_2</t>
+  </si>
+  <si>
+    <t>1_google4999|2_ios4999</t>
+  </si>
+  <si>
+    <t>1990000_167978000|1022502_10|1010302_2</t>
+  </si>
+  <si>
+    <t>1990000_177976000|1022502_10|1010302_2</t>
+  </si>
+  <si>
+    <t>1990000_187974000|1022502_10|1010302_2</t>
+  </si>
+  <si>
+    <t>1990000_197972000|1022502_10|1010302_2</t>
+  </si>
+  <si>
+    <t>1990000_414980000|1022502_20|1010303_2</t>
+  </si>
+  <si>
+    <t>1_google9999|2_ios9999</t>
+  </si>
+  <si>
+    <t>1990000_434978000|1022502_20|1010303_2</t>
+  </si>
+  <si>
+    <t>1990000_454976000|1022502_20|1010303_2</t>
+  </si>
+  <si>
+    <t>1990000_474974000|1022502_20|1010303_2</t>
+  </si>
+  <si>
+    <t>1990000_494972000|1022502_20|1010303_2</t>
   </si>
 </sst>
 </file>
@@ -137,7 +209,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -295,8 +367,19 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="35">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -305,7 +388,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.6"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -390,12 +473,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -718,58 +795,58 @@
     <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -786,13 +863,13 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1106,18 +1183,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E24"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="4"/>
+  <dimension ref="A1:F24"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="12.35" style="1" customWidth="1"/>
-    <col min="2" max="2" width="15.4416666666667" style="1" customWidth="1"/>
-    <col min="3" max="3" width="50.2916666666667" style="1" customWidth="1"/>
+    <col min="1" max="1" width="12.375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5" style="1" customWidth="1"/>
+    <col min="3" max="3" width="50.25" style="1" customWidth="1"/>
     <col min="4" max="4" width="14.375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="14.1166666666667" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9" style="1"/>
+    <col min="5" max="5" width="14.125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="25.75" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1133,46 +1211,55 @@
       <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5">
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="E2" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>11</v>
+        <v>13</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="6"/>
       <c r="B4" s="6"/>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:6">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -1180,7 +1267,7 @@
         <v>10</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D5" s="1">
         <v>120</v>
@@ -1188,8 +1275,11 @@
       <c r="E5" s="1">
         <v>0.99</v>
       </c>
-    </row>
-    <row r="6" spans="1:5">
+      <c r="F5" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
       <c r="A6" s="1">
         <v>2</v>
       </c>
@@ -1197,7 +1287,7 @@
         <v>20</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D6" s="1">
         <v>120</v>
@@ -1205,8 +1295,11 @@
       <c r="E6" s="1">
         <v>0.99</v>
       </c>
-    </row>
-    <row r="7" spans="1:5">
+      <c r="F6" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
       <c r="A7" s="1">
         <v>3</v>
       </c>
@@ -1214,16 +1307,19 @@
         <v>30</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D7" s="1">
         <v>120</v>
       </c>
       <c r="E7" s="1">
-        <v>0.99</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
+        <v>1.99</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
       <c r="A8" s="1">
         <v>4</v>
       </c>
@@ -1231,16 +1327,19 @@
         <v>40</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D8" s="1">
         <v>120</v>
       </c>
       <c r="E8" s="1">
-        <v>4.99</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
+        <v>2.99</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
       <c r="A9" s="1">
         <v>5</v>
       </c>
@@ -1248,16 +1347,19 @@
         <v>50</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D9" s="1">
         <v>120</v>
       </c>
       <c r="E9" s="1">
-        <v>4.99</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
+        <v>5.99</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
       <c r="A10" s="1">
         <v>6</v>
       </c>
@@ -1265,16 +1367,19 @@
         <v>60</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="D10" s="1">
         <v>120</v>
       </c>
       <c r="E10" s="1">
-        <v>4.99</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
+        <v>7.99</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
       <c r="A11" s="1">
         <v>7</v>
       </c>
@@ -1282,16 +1387,19 @@
         <v>70</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="D11" s="1">
         <v>120</v>
       </c>
       <c r="E11" s="1">
-        <v>4.99</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
+        <v>9.99</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
       <c r="A12" s="1">
         <v>8</v>
       </c>
@@ -1299,16 +1407,19 @@
         <v>80</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="D12" s="1">
         <v>120</v>
       </c>
       <c r="E12" s="1">
-        <v>9.99</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
+        <v>14.99</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
       <c r="A13" s="1">
         <v>9</v>
       </c>
@@ -1316,16 +1427,19 @@
         <v>90</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="D13" s="1">
         <v>120</v>
       </c>
       <c r="E13" s="1">
-        <v>9.99</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
+        <v>19.99</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
       <c r="A14" s="1">
         <v>10</v>
       </c>
@@ -1333,16 +1447,19 @@
         <v>100</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="D14" s="1">
         <v>120</v>
       </c>
       <c r="E14" s="1">
-        <v>9.99</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
+        <v>24.99</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
       <c r="A15" s="1">
         <v>11</v>
       </c>
@@ -1350,16 +1467,19 @@
         <v>110</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="D15" s="1">
         <v>120</v>
       </c>
       <c r="E15" s="1">
-        <v>9.99</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
+        <v>49.99</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
       <c r="A16" s="1">
         <v>12</v>
       </c>
@@ -1367,16 +1487,19 @@
         <v>120</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="D16" s="1">
         <v>120</v>
       </c>
       <c r="E16" s="1">
-        <v>9.99</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
+        <v>49.99</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
       <c r="A17" s="1">
         <v>13</v>
       </c>
@@ -1384,16 +1507,19 @@
         <v>130</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="D17" s="1">
         <v>120</v>
       </c>
       <c r="E17" s="1">
-        <v>9.99</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
+        <v>49.99</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
       <c r="A18" s="1">
         <v>14</v>
       </c>
@@ -1401,16 +1527,19 @@
         <v>140</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="D18" s="1">
         <v>120</v>
       </c>
       <c r="E18" s="1">
-        <v>29.99</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
+        <v>49.99</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
       <c r="A19" s="1">
         <v>15</v>
       </c>
@@ -1418,16 +1547,19 @@
         <v>150</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="D19" s="1">
         <v>120</v>
       </c>
       <c r="E19" s="1">
-        <v>29.99</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
+        <v>49.99</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
       <c r="A20" s="1">
         <v>16</v>
       </c>
@@ -1435,16 +1567,19 @@
         <v>160</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="D20" s="1">
         <v>120</v>
       </c>
       <c r="E20" s="1">
-        <v>29.99</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
+        <v>99.99</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
       <c r="A21" s="1">
         <v>17</v>
       </c>
@@ -1452,16 +1587,19 @@
         <v>170</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="D21" s="1">
         <v>120</v>
       </c>
       <c r="E21" s="1">
-        <v>29.99</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
+        <v>99.99</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
       <c r="A22" s="1">
         <v>18</v>
       </c>
@@ -1469,7 +1607,7 @@
         <v>180</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="D22" s="1">
         <v>120</v>
@@ -1477,8 +1615,11 @@
       <c r="E22" s="1">
         <v>99.99</v>
       </c>
-    </row>
-    <row r="23" spans="1:5">
+      <c r="F22" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
       <c r="A23" s="1">
         <v>19</v>
       </c>
@@ -1486,7 +1627,7 @@
         <v>190</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="D23" s="1">
         <v>120</v>
@@ -1494,8 +1635,11 @@
       <c r="E23" s="1">
         <v>99.99</v>
       </c>
-    </row>
-    <row r="24" spans="1:5">
+      <c r="F23" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
       <c r="A24" s="1">
         <v>20</v>
       </c>
@@ -1503,19 +1647,23 @@
         <v>200</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="D24" s="1">
         <v>120</v>
       </c>
       <c r="E24" s="1">
         <v>99.99</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 

--- a/slots/resources/sample/PlayerLevelPack.xlsx
+++ b/slots/resources/sample/PlayerLevelPack.xlsx
@@ -121,82 +121,82 @@
     <t>1_google199|2_ios199</t>
   </si>
   <si>
+    <t>1990000_4777000|1022502_2</t>
+  </si>
+  <si>
     <t>1990000_7277000|1022502_2</t>
   </si>
   <si>
     <t>1_googl299|2_ios299</t>
   </si>
   <si>
-    <t>1990000_14777000|1022502_2</t>
+    <t>1990000_7576000|1022502_2</t>
+  </si>
+  <si>
+    <t>1990000_13275000|1022502_2</t>
+  </si>
+  <si>
+    <t>1_google499|2_ios499</t>
+  </si>
+  <si>
+    <t>1990000_16277000|1022502_5</t>
   </si>
   <si>
     <t>1_google599|2_ios599</t>
   </si>
   <si>
-    <t>1990000_20576000|1022502_2</t>
+    <t>1990000_22477000|1022502_5|1010301_1</t>
   </si>
   <si>
     <t>1_google799|2_ios799</t>
   </si>
   <si>
-    <t>1990000_26775000|1022502_2</t>
+    <t>1990000_29077000|1022502_5|1010301_2</t>
   </si>
   <si>
     <t>1_google999|2_ios999</t>
   </si>
   <si>
-    <t>1990000_41477000|1022502_5</t>
+    <t>1990000_29980000|1022502_10|1010302_2</t>
+  </si>
+  <si>
+    <t>1990000_48978000|1022502_10|1010302_2</t>
   </si>
   <si>
     <t>1_google1499|2_ios1499</t>
   </si>
   <si>
-    <t>1990000_57277000|1022502_5|1010301_1</t>
+    <t>1990000_51976000|1022502_10|1010302_2</t>
+  </si>
+  <si>
+    <t>1990000_73974000|1022502_10|1010302_2</t>
   </si>
   <si>
     <t>1_google1999|2_ios1999</t>
   </si>
   <si>
-    <t>1990000_74077000|1022502_5|1010301_2</t>
+    <t>1990000_77972000|1022502_10|1010302_2</t>
+  </si>
+  <si>
+    <t>1990000_99980000|1022502_20|1010303_2</t>
   </si>
   <si>
     <t>1_google2499|2_ios2499</t>
   </si>
   <si>
-    <t>1990000_157980000|1022502_10|1010302_2</t>
+    <t>1990000_104978000|1022502_20|1010303_2</t>
+  </si>
+  <si>
+    <t>1990000_224976000|1022502_20|1010303_2</t>
   </si>
   <si>
     <t>1_google4999|2_ios4999</t>
   </si>
   <si>
-    <t>1990000_167978000|1022502_10|1010302_2</t>
-  </si>
-  <si>
-    <t>1990000_177976000|1022502_10|1010302_2</t>
-  </si>
-  <si>
-    <t>1990000_187974000|1022502_10|1010302_2</t>
-  </si>
-  <si>
-    <t>1990000_197972000|1022502_10|1010302_2</t>
-  </si>
-  <si>
-    <t>1990000_414980000|1022502_20|1010303_2</t>
-  </si>
-  <si>
-    <t>1_google9999|2_ios9999</t>
-  </si>
-  <si>
-    <t>1990000_434978000|1022502_20|1010303_2</t>
-  </si>
-  <si>
-    <t>1990000_454976000|1022502_20|1010303_2</t>
-  </si>
-  <si>
-    <t>1990000_474974000|1022502_20|1010303_2</t>
-  </si>
-  <si>
-    <t>1990000_494972000|1022502_20|1010303_2</t>
+    <t>1990000_234974000|1022502_20|1010303_2</t>
+  </si>
+  <si>
+    <t>1990000_244972000|1022502_20|1010303_2</t>
   </si>
 </sst>
 </file>
@@ -1333,10 +1333,10 @@
         <v>120</v>
       </c>
       <c r="E8" s="1">
-        <v>2.99</v>
+        <v>1.99</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1347,16 +1347,16 @@
         <v>50</v>
       </c>
       <c r="C9" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D9" s="1">
+        <v>120</v>
+      </c>
+      <c r="E9" s="1">
+        <v>2.99</v>
+      </c>
+      <c r="F9" s="1" t="s">
         <v>21</v>
-      </c>
-      <c r="D9" s="1">
-        <v>120</v>
-      </c>
-      <c r="E9" s="1">
-        <v>5.99</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1367,16 +1367,16 @@
         <v>60</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D10" s="1">
         <v>120</v>
       </c>
       <c r="E10" s="1">
-        <v>7.99</v>
+        <v>2.99</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1387,16 +1387,16 @@
         <v>70</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D11" s="1">
         <v>120</v>
       </c>
       <c r="E11" s="1">
-        <v>9.99</v>
+        <v>4.99</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1407,16 +1407,16 @@
         <v>80</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D12" s="1">
         <v>120</v>
       </c>
       <c r="E12" s="1">
-        <v>14.99</v>
+        <v>5.99</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1427,16 +1427,16 @@
         <v>90</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D13" s="1">
         <v>120</v>
       </c>
       <c r="E13" s="1">
-        <v>19.99</v>
+        <v>7.99</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1447,16 +1447,16 @@
         <v>100</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D14" s="1">
         <v>120</v>
       </c>
       <c r="E14" s="1">
-        <v>24.99</v>
+        <v>9.99</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1467,16 +1467,16 @@
         <v>110</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D15" s="1">
         <v>120</v>
       </c>
       <c r="E15" s="1">
-        <v>49.99</v>
+        <v>9.99</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1487,16 +1487,16 @@
         <v>120</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D16" s="1">
         <v>120</v>
       </c>
       <c r="E16" s="1">
-        <v>49.99</v>
+        <v>14.99</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -1507,16 +1507,16 @@
         <v>130</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D17" s="1">
         <v>120</v>
       </c>
       <c r="E17" s="1">
-        <v>49.99</v>
+        <v>14.99</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -1527,16 +1527,16 @@
         <v>140</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D18" s="1">
         <v>120</v>
       </c>
       <c r="E18" s="1">
-        <v>49.99</v>
+        <v>19.99</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -1547,16 +1547,16 @@
         <v>150</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D19" s="1">
         <v>120</v>
       </c>
       <c r="E19" s="1">
-        <v>49.99</v>
+        <v>19.99</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -1567,16 +1567,16 @@
         <v>160</v>
       </c>
       <c r="C20" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D20" s="1">
+        <v>120</v>
+      </c>
+      <c r="E20" s="1">
+        <v>24.99</v>
+      </c>
+      <c r="F20" s="1" t="s">
         <v>39</v>
-      </c>
-      <c r="D20" s="1">
-        <v>120</v>
-      </c>
-      <c r="E20" s="1">
-        <v>99.99</v>
-      </c>
-      <c r="F20" s="1" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -1587,16 +1587,16 @@
         <v>170</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D21" s="1">
         <v>120</v>
       </c>
       <c r="E21" s="1">
-        <v>99.99</v>
+        <v>24.99</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -1607,16 +1607,16 @@
         <v>180</v>
       </c>
       <c r="C22" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D22" s="1">
+        <v>120</v>
+      </c>
+      <c r="E22" s="1">
+        <v>49.99</v>
+      </c>
+      <c r="F22" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="D22" s="1">
-        <v>120</v>
-      </c>
-      <c r="E22" s="1">
-        <v>99.99</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -1633,10 +1633,10 @@
         <v>120</v>
       </c>
       <c r="E23" s="1">
-        <v>99.99</v>
+        <v>49.99</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -1653,10 +1653,10 @@
         <v>120</v>
       </c>
       <c r="E24" s="1">
-        <v>99.99</v>
+        <v>49.99</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/PlayerLevelPack.xlsx
+++ b/slots/resources/sample/PlayerLevelPack.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29231"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\java\gamedoc\游戏配置表\common\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4A6CC1C-0EE6-4235-ACA7-14CC76D6BA84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="PlayerLevelPack" sheetId="1" r:id="rId1"/>
@@ -34,8 +28,41 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Administrator</author>
+  </authors>
+  <commentList>
+    <comment ref="F1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+1_1|2_2 ： 渠道1id_对应的商品id|渠道2id_对应的商品id
+注：1 =  google渠道ID；2 = apple 渠道ID</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="45">
   <si>
     <t>id</t>
   </si>
@@ -52,6 +79,9 @@
     <t>购买金额</t>
   </si>
   <si>
+    <t>渠道商品ID</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
@@ -61,6 +91,9 @@
     <t>BigDecimal</t>
   </si>
   <si>
+    <t>map&lt;int{_}String&gt;{|}</t>
+  </si>
+  <si>
     <t>playerlevel</t>
   </si>
   <si>
@@ -73,36 +106,69 @@
     <t>pay</t>
   </si>
   <si>
+    <t>channelCommodity</t>
+  </si>
+  <si>
     <t>1990000_2475000</t>
   </si>
   <si>
+    <t>1_google99|2_ios99</t>
+  </si>
+  <si>
     <t>1990000_4975000</t>
   </si>
   <si>
+    <t>1_google199|2_ios199</t>
+  </si>
+  <si>
     <t>1990000_7277000|1022502_2</t>
   </si>
   <si>
+    <t>1_googl299|2_ios299</t>
+  </si>
+  <si>
     <t>1990000_14777000|1022502_2</t>
   </si>
   <si>
+    <t>1_google599|2_ios599</t>
+  </si>
+  <si>
     <t>1990000_20576000|1022502_2</t>
   </si>
   <si>
+    <t>1_google799|2_ios799</t>
+  </si>
+  <si>
     <t>1990000_26775000|1022502_2</t>
   </si>
   <si>
+    <t>1_google999|2_ios999</t>
+  </si>
+  <si>
     <t>1990000_41477000|1022502_5</t>
   </si>
   <si>
+    <t>1_google1499|2_ios1499</t>
+  </si>
+  <si>
     <t>1990000_57277000|1022502_5|1010301_1</t>
   </si>
   <si>
+    <t>1_google1999|2_ios1999</t>
+  </si>
+  <si>
     <t>1990000_74077000|1022502_5|1010301_2</t>
   </si>
   <si>
+    <t>1_google2499|2_ios2499</t>
+  </si>
+  <si>
     <t>1990000_157980000|1022502_10|1010302_2</t>
   </si>
   <si>
+    <t>1_google4999|2_ios4999</t>
+  </si>
+  <si>
     <t>1990000_167978000|1022502_10|1010302_2</t>
   </si>
   <si>
@@ -118,6 +184,9 @@
     <t>1990000_414980000|1022502_20|1010303_2</t>
   </si>
   <si>
+    <t>1_google9999|2_ios9999</t>
+  </si>
+  <si>
     <t>1990000_434978000|1022502_20|1010303_2</t>
   </si>
   <si>
@@ -128,82 +197,19 @@
   </si>
   <si>
     <t>1990000_494972000|1022502_20|1010303_2</t>
-  </si>
-  <si>
-    <t>渠道商品ID</t>
-  </si>
-  <si>
-    <t>map&lt;int{_}String&gt;{|}</t>
-  </si>
-  <si>
-    <t>channelCommodity</t>
-  </si>
-  <si>
-    <t>1_1|2_2</t>
-  </si>
-  <si>
-    <t>1_1|2_3</t>
-  </si>
-  <si>
-    <t>1_1|2_4</t>
-  </si>
-  <si>
-    <t>1_1|2_5</t>
-  </si>
-  <si>
-    <t>1_1|2_6</t>
-  </si>
-  <si>
-    <t>1_1|2_7</t>
-  </si>
-  <si>
-    <t>1_1|2_8</t>
-  </si>
-  <si>
-    <t>1_1|2_9</t>
-  </si>
-  <si>
-    <t>1_1|2_10</t>
-  </si>
-  <si>
-    <t>1_1|2_11</t>
-  </si>
-  <si>
-    <t>1_1|2_12</t>
-  </si>
-  <si>
-    <t>1_1|2_13</t>
-  </si>
-  <si>
-    <t>1_1|2_14</t>
-  </si>
-  <si>
-    <t>1_1|2_15</t>
-  </si>
-  <si>
-    <t>1_1|2_16</t>
-  </si>
-  <si>
-    <t>1_1|2_17</t>
-  </si>
-  <si>
-    <t>1_1|2_18</t>
-  </si>
-  <si>
-    <t>1_1|2_19</t>
-  </si>
-  <si>
-    <t>1_1|2_20</t>
-  </si>
-  <si>
-    <t>1_1|2_21</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -218,13 +224,162 @@
       <charset val="134"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -233,7 +388,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -243,8 +398,188 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -267,9 +602,251 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -296,17 +873,61 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -556,25 +1177,25 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:F24"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="12.375" style="1" customWidth="1"/>
     <col min="2" max="2" width="15.5" style="1" customWidth="1"/>
     <col min="3" max="3" width="50.25" style="1" customWidth="1"/>
     <col min="4" max="4" width="14.375" style="1" customWidth="1"/>
     <col min="5" max="5" width="14.125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="21.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="25.75" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:6">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -591,54 +1212,54 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="E2" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.15">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.15">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
       <c r="A4" s="6"/>
       <c r="B4" s="6"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:6">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -646,7 +1267,7 @@
         <v>10</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D5" s="1">
         <v>120</v>
@@ -655,10 +1276,10 @@
         <v>0.99</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.15">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
       <c r="A6" s="1">
         <v>2</v>
       </c>
@@ -666,7 +1287,7 @@
         <v>20</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D6" s="1">
         <v>120</v>
@@ -675,10 +1296,10 @@
         <v>0.99</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.15">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
       <c r="A7" s="1">
         <v>3</v>
       </c>
@@ -686,7 +1307,7 @@
         <v>30</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D7" s="1">
         <v>120</v>
@@ -695,10 +1316,10 @@
         <v>1.99</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.15">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
       <c r="A8" s="1">
         <v>4</v>
       </c>
@@ -706,7 +1327,7 @@
         <v>40</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D8" s="1">
         <v>120</v>
@@ -715,10 +1336,10 @@
         <v>2.99</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.15">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
       <c r="A9" s="1">
         <v>5</v>
       </c>
@@ -726,7 +1347,7 @@
         <v>50</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="D9" s="1">
         <v>120</v>
@@ -735,10 +1356,10 @@
         <v>5.99</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.15">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
       <c r="A10" s="1">
         <v>6</v>
       </c>
@@ -746,7 +1367,7 @@
         <v>60</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="D10" s="1">
         <v>120</v>
@@ -755,10 +1376,10 @@
         <v>7.99</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.15">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
       <c r="A11" s="1">
         <v>7</v>
       </c>
@@ -766,7 +1387,7 @@
         <v>70</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D11" s="1">
         <v>120</v>
@@ -775,10 +1396,10 @@
         <v>9.99</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.15">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
       <c r="A12" s="1">
         <v>8</v>
       </c>
@@ -786,7 +1407,7 @@
         <v>80</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="D12" s="1">
         <v>120</v>
@@ -795,10 +1416,10 @@
         <v>14.99</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.15">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
       <c r="A13" s="1">
         <v>9</v>
       </c>
@@ -806,19 +1427,19 @@
         <v>90</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="D13" s="1">
         <v>120</v>
       </c>
       <c r="E13" s="1">
-        <v>19.989999999999998</v>
+        <v>19.99</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.15">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
       <c r="A14" s="1">
         <v>10</v>
       </c>
@@ -826,7 +1447,7 @@
         <v>100</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="D14" s="1">
         <v>120</v>
@@ -835,10 +1456,10 @@
         <v>24.99</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.15">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
       <c r="A15" s="1">
         <v>11</v>
       </c>
@@ -846,7 +1467,7 @@
         <v>110</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="D15" s="1">
         <v>120</v>
@@ -855,10 +1476,10 @@
         <v>49.99</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.15">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
       <c r="A16" s="1">
         <v>12</v>
       </c>
@@ -866,7 +1487,7 @@
         <v>120</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="D16" s="1">
         <v>120</v>
@@ -875,10 +1496,10 @@
         <v>49.99</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.15">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
       <c r="A17" s="1">
         <v>13</v>
       </c>
@@ -886,7 +1507,7 @@
         <v>130</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="D17" s="1">
         <v>120</v>
@@ -895,10 +1516,10 @@
         <v>49.99</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.15">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
       <c r="A18" s="1">
         <v>14</v>
       </c>
@@ -906,7 +1527,7 @@
         <v>140</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="D18" s="1">
         <v>120</v>
@@ -915,10 +1536,10 @@
         <v>49.99</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.15">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
       <c r="A19" s="1">
         <v>15</v>
       </c>
@@ -926,7 +1547,7 @@
         <v>150</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="D19" s="1">
         <v>120</v>
@@ -935,10 +1556,10 @@
         <v>49.99</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.15">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
       <c r="A20" s="1">
         <v>16</v>
       </c>
@@ -946,7 +1567,7 @@
         <v>160</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="D20" s="1">
         <v>120</v>
@@ -955,10 +1576,10 @@
         <v>99.99</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.15">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
       <c r="A21" s="1">
         <v>17</v>
       </c>
@@ -966,7 +1587,7 @@
         <v>170</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="D21" s="1">
         <v>120</v>
@@ -975,10 +1596,10 @@
         <v>99.99</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.15">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
       <c r="A22" s="1">
         <v>18</v>
       </c>
@@ -986,7 +1607,7 @@
         <v>180</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="D22" s="1">
         <v>120</v>
@@ -995,10 +1616,10 @@
         <v>99.99</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.15">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
       <c r="A23" s="1">
         <v>19</v>
       </c>
@@ -1006,7 +1627,7 @@
         <v>190</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="D23" s="1">
         <v>120</v>
@@ -1015,10 +1636,10 @@
         <v>99.99</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.15">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
       <c r="A24" s="1">
         <v>20</v>
       </c>
@@ -1026,7 +1647,7 @@
         <v>200</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="D24" s="1">
         <v>120</v>
@@ -1035,34 +1656,37 @@
         <v>99.99</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData/>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData/>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/slots/resources/sample/PlayerLevelPack.xlsx
+++ b/slots/resources/sample/PlayerLevelPack.xlsx
@@ -109,94 +109,94 @@
     <t>channelCommodity</t>
   </si>
   <si>
-    <t>1990000_2475000</t>
+    <t>1990000_17325000</t>
   </si>
   <si>
     <t>1_google99|2_ios99</t>
   </si>
   <si>
-    <t>1990000_4975000</t>
+    <t>1990000_34825000</t>
   </si>
   <si>
     <t>1_google199|2_ios199</t>
   </si>
   <si>
-    <t>1990000_4777000|1022502_2</t>
-  </si>
-  <si>
-    <t>1990000_7277000|1022502_2</t>
+    <t>1990000_33439000|1022502_2</t>
+  </si>
+  <si>
+    <t>1990000_50939000|1022502_2</t>
   </si>
   <si>
     <t>1_googl299|2_ios299</t>
   </si>
   <si>
-    <t>1990000_7576000|1022502_2</t>
-  </si>
-  <si>
-    <t>1990000_13275000|1022502_2</t>
+    <t>1990000_53032000|1022502_2</t>
+  </si>
+  <si>
+    <t>1990000_92925000|1022502_2</t>
   </si>
   <si>
     <t>1_google499|2_ios499</t>
   </si>
   <si>
-    <t>1990000_16277000|1022502_5</t>
+    <t>1990000_113939000|1022502_5</t>
   </si>
   <si>
     <t>1_google599|2_ios599</t>
   </si>
   <si>
-    <t>1990000_22477000|1022502_5|1010301_1</t>
+    <t>1990000_157339000|1022502_5|1010301_1</t>
   </si>
   <si>
     <t>1_google799|2_ios799</t>
   </si>
   <si>
-    <t>1990000_29077000|1022502_5|1010301_2</t>
+    <t>1990000_203539000|1022502_5|1010301_2</t>
   </si>
   <si>
     <t>1_google999|2_ios999</t>
   </si>
   <si>
-    <t>1990000_29980000|1022502_10|1010302_2</t>
-  </si>
-  <si>
-    <t>1990000_48978000|1022502_10|1010302_2</t>
+    <t>1990000_209860000|1022502_10|1010302_2</t>
+  </si>
+  <si>
+    <t>1990000_342846000|1022502_10|1010302_2</t>
   </si>
   <si>
     <t>1_google1499|2_ios1499</t>
   </si>
   <si>
-    <t>1990000_51976000|1022502_10|1010302_2</t>
-  </si>
-  <si>
-    <t>1990000_73974000|1022502_10|1010302_2</t>
+    <t>1990000_363832000|1022502_10|1010302_2</t>
+  </si>
+  <si>
+    <t>1990000_517818000|1022502_10|1010302_2</t>
   </si>
   <si>
     <t>1_google1999|2_ios1999</t>
   </si>
   <si>
-    <t>1990000_77972000|1022502_10|1010302_2</t>
-  </si>
-  <si>
-    <t>1990000_99980000|1022502_20|1010303_2</t>
+    <t>1990000_545804000|1022502_10|1010302_2</t>
+  </si>
+  <si>
+    <t>1990000_699860000|1022502_20|1010303_2</t>
   </si>
   <si>
     <t>1_google2499|2_ios2499</t>
   </si>
   <si>
-    <t>1990000_104978000|1022502_20|1010303_2</t>
-  </si>
-  <si>
-    <t>1990000_224976000|1022502_20|1010303_2</t>
+    <t>1990000_734846000|1022502_20|1010303_2</t>
+  </si>
+  <si>
+    <t>1990000_1574832000|1022502_20|1010303_2</t>
   </si>
   <si>
     <t>1_google4999|2_ios4999</t>
   </si>
   <si>
-    <t>1990000_234974000|1022502_20|1010303_2</t>
-  </si>
-  <si>
-    <t>1990000_244972000|1022502_20|1010303_2</t>
+    <t>1990000_1644818000|1022502_20|1010303_2</t>
+  </si>
+  <si>
+    <t>1990000_1714804000|1022502_20|1010303_2</t>
   </si>
 </sst>
 </file>
@@ -368,12 +368,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1255,7 +1255,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:6">
       <c r="A4" s="6"/>
       <c r="B4" s="6"/>
     </row>

--- a/slots/resources/sample/PlayerLevelPack.xlsx
+++ b/slots/resources/sample/PlayerLevelPack.xlsx
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="39">
   <si>
     <t>id</t>
   </si>
@@ -109,94 +109,76 @@
     <t>channelCommodity</t>
   </si>
   <si>
-    <t>1990000_17325000</t>
+    <t>1990000_6930000</t>
   </si>
   <si>
     <t>1_google99|2_ios99</t>
   </si>
   <si>
-    <t>1990000_34825000</t>
+    <t>1990000_13930000</t>
   </si>
   <si>
     <t>1_google199|2_ios199</t>
   </si>
   <si>
-    <t>1990000_33439000|1022502_2</t>
-  </si>
-  <si>
-    <t>1990000_50939000|1022502_2</t>
+    <t>1990000_12544000|1022502_2</t>
+  </si>
+  <si>
+    <t>1990000_19544000|1022502_2</t>
   </si>
   <si>
     <t>1_googl299|2_ios299</t>
   </si>
   <si>
-    <t>1990000_53032000|1022502_2</t>
-  </si>
-  <si>
-    <t>1990000_92925000|1022502_2</t>
+    <t>1990000_30051000|1022502_2</t>
   </si>
   <si>
     <t>1_google499|2_ios499</t>
   </si>
   <si>
-    <t>1990000_113939000|1022502_5</t>
+    <t>1990000_30079000|1022502_5</t>
   </si>
   <si>
     <t>1_google599|2_ios599</t>
   </si>
   <si>
-    <t>1990000_157339000|1022502_5|1010301_1</t>
+    <t>1990000_41253000|1022502_5|1010301_1</t>
   </si>
   <si>
     <t>1_google799|2_ios799</t>
   </si>
   <si>
-    <t>1990000_203539000|1022502_5|1010301_2</t>
+    <t>1990000_45435000|1022502_5|1010301_2</t>
   </si>
   <si>
     <t>1_google999|2_ios999</t>
   </si>
   <si>
-    <t>1990000_209860000|1022502_10|1010302_2</t>
-  </si>
-  <si>
-    <t>1990000_342846000|1022502_10|1010302_2</t>
+    <t>1990000_41960000|1022502_10|1010302_2</t>
+  </si>
+  <si>
+    <t>1990000_55967000|1022502_10|1010302_2</t>
   </si>
   <si>
     <t>1_google1499|2_ios1499</t>
   </si>
   <si>
-    <t>1990000_363832000|1022502_10|1010302_2</t>
-  </si>
-  <si>
-    <t>1990000_517818000|1022502_10|1010302_2</t>
+    <t>1990000_62974000|1022502_10|1010302_2</t>
   </si>
   <si>
     <t>1_google1999|2_ios1999</t>
   </si>
   <si>
-    <t>1990000_545804000|1022502_10|1010302_2</t>
-  </si>
-  <si>
-    <t>1990000_699860000|1022502_20|1010303_2</t>
+    <t>1990000_64778000|1022502_20|1010303_2</t>
   </si>
   <si>
     <t>1_google2499|2_ios2499</t>
   </si>
   <si>
-    <t>1990000_734846000|1022502_20|1010303_2</t>
-  </si>
-  <si>
-    <t>1990000_1574832000|1022502_20|1010303_2</t>
+    <t>1990000_91038000|1022502_20|1010303_2</t>
   </si>
   <si>
     <t>1_google4999|2_ios4999</t>
-  </si>
-  <si>
-    <t>1990000_1644818000|1022502_20|1010303_2</t>
-  </si>
-  <si>
-    <t>1990000_1714804000|1022502_20|1010303_2</t>
   </si>
 </sst>
 </file>
@@ -368,12 +350,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1367,7 +1349,7 @@
         <v>60</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D10" s="1">
         <v>120</v>
@@ -1387,7 +1369,7 @@
         <v>70</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D11" s="1">
         <v>120</v>
@@ -1396,7 +1378,7 @@
         <v>4.99</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1407,7 +1389,7 @@
         <v>80</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D12" s="1">
         <v>120</v>
@@ -1416,7 +1398,7 @@
         <v>5.99</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1427,7 +1409,7 @@
         <v>90</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D13" s="1">
         <v>120</v>
@@ -1436,7 +1418,7 @@
         <v>7.99</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1447,7 +1429,7 @@
         <v>100</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D14" s="1">
         <v>120</v>
@@ -1456,7 +1438,7 @@
         <v>9.99</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1467,7 +1449,7 @@
         <v>110</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D15" s="1">
         <v>120</v>
@@ -1476,7 +1458,7 @@
         <v>9.99</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1487,7 +1469,7 @@
         <v>120</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D16" s="1">
         <v>120</v>
@@ -1496,7 +1478,7 @@
         <v>14.99</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -1507,7 +1489,7 @@
         <v>130</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D17" s="1">
         <v>120</v>
@@ -1516,7 +1498,7 @@
         <v>14.99</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -1527,7 +1509,7 @@
         <v>140</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D18" s="1">
         <v>120</v>
@@ -1536,7 +1518,7 @@
         <v>19.99</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -1547,7 +1529,7 @@
         <v>150</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="D19" s="1">
         <v>120</v>
@@ -1556,7 +1538,7 @@
         <v>19.99</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -1567,7 +1549,7 @@
         <v>160</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D20" s="1">
         <v>120</v>
@@ -1576,7 +1558,7 @@
         <v>24.99</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -1587,7 +1569,7 @@
         <v>170</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="D21" s="1">
         <v>120</v>
@@ -1596,7 +1578,7 @@
         <v>24.99</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -1607,7 +1589,7 @@
         <v>180</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="D22" s="1">
         <v>120</v>
@@ -1616,7 +1598,7 @@
         <v>49.99</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -1627,7 +1609,7 @@
         <v>190</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="D23" s="1">
         <v>120</v>
@@ -1636,7 +1618,7 @@
         <v>49.99</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -1647,7 +1629,7 @@
         <v>200</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="D24" s="1">
         <v>120</v>
@@ -1656,7 +1638,7 @@
         <v>49.99</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/PlayerLevelPack.xlsx
+++ b/slots/resources/sample/PlayerLevelPack.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="PlayerLevelPack" sheetId="1" r:id="rId1"/>
@@ -109,73 +109,73 @@
     <t>channelCommodity</t>
   </si>
   <si>
-    <t>1990000_6930000</t>
+    <t>1990000_297000</t>
   </si>
   <si>
     <t>1_google99|2_ios99</t>
   </si>
   <si>
-    <t>1990000_13930000</t>
+    <t>1990000_597000</t>
   </si>
   <si>
     <t>1_google199|2_ios199</t>
   </si>
   <si>
-    <t>1990000_12544000|1022502_2</t>
-  </si>
-  <si>
-    <t>1990000_19544000|1022502_2</t>
+    <t>1990000_567000|1022502_2</t>
+  </si>
+  <si>
+    <t>1990000_867000|1022502_2</t>
   </si>
   <si>
     <t>1_googl299|2_ios299</t>
   </si>
   <si>
-    <t>1990000_30051000|1022502_2</t>
+    <t>1990000_1317000|1022502_2</t>
   </si>
   <si>
     <t>1_google499|2_ios499</t>
   </si>
   <si>
-    <t>1990000_30079000|1022502_5</t>
+    <t>1990000_1363000|1022502_5</t>
   </si>
   <si>
     <t>1_google599|2_ios599</t>
   </si>
   <si>
-    <t>1990000_41253000|1022502_5|1010301_1</t>
+    <t>1990000_1840000|1022502_5|1010301_1</t>
   </si>
   <si>
     <t>1_google799|2_ios799</t>
   </si>
   <si>
-    <t>1990000_45435000|1022502_5|1010301_2</t>
+    <t>1990000_2017000|1022502_5|1010301_2</t>
   </si>
   <si>
     <t>1_google999|2_ios999</t>
   </si>
   <si>
-    <t>1990000_41960000|1022502_10|1010302_2</t>
-  </si>
-  <si>
-    <t>1990000_55967000|1022502_10|1010302_2</t>
+    <t>1990000_1937000|1022502_10|1010302_2</t>
+  </si>
+  <si>
+    <t>1990000_2537000|1022502_10|1010302_2</t>
   </si>
   <si>
     <t>1_google1499|2_ios1499</t>
   </si>
   <si>
-    <t>1990000_62974000|1022502_10|1010302_2</t>
+    <t>1990000_2838000|1022502_10|1010302_2</t>
   </si>
   <si>
     <t>1_google1999|2_ios1999</t>
   </si>
   <si>
-    <t>1990000_64778000|1022502_20|1010303_2</t>
+    <t>1990000_3041000|1022502_20|1010303_2</t>
   </si>
   <si>
     <t>1_google2499|2_ios2499</t>
   </si>
   <si>
-    <t>1990000_91038000|1022502_20|1010303_2</t>
+    <t>1990000_4166000|1022502_20|1010303_2</t>
   </si>
   <si>
     <t>1_google4999|2_ios4999</t>

--- a/slots/resources/sample/PlayerLevelPack.xlsx
+++ b/slots/resources/sample/PlayerLevelPack.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11925"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="PlayerLevelPack" sheetId="1" r:id="rId1"/>
@@ -109,73 +109,73 @@
     <t>channelCommodity</t>
   </si>
   <si>
-    <t>1990000_297000</t>
+    <t>1990000_6930000</t>
   </si>
   <si>
     <t>1_google99|2_ios99</t>
   </si>
   <si>
-    <t>1990000_597000</t>
+    <t>1990000_13930000</t>
   </si>
   <si>
     <t>1_google199|2_ios199</t>
   </si>
   <si>
-    <t>1990000_567000|1022502_2</t>
-  </si>
-  <si>
-    <t>1990000_867000|1022502_2</t>
+    <t>1990000_12544000|1022502_2</t>
+  </si>
+  <si>
+    <t>1990000_19544000|1022502_2</t>
   </si>
   <si>
     <t>1_googl299|2_ios299</t>
   </si>
   <si>
-    <t>1990000_1317000|1022502_2</t>
+    <t>1990000_30051000|1022502_2</t>
   </si>
   <si>
     <t>1_google499|2_ios499</t>
   </si>
   <si>
-    <t>1990000_1363000|1022502_5</t>
+    <t>1990000_30079000|1022502_5</t>
   </si>
   <si>
     <t>1_google599|2_ios599</t>
   </si>
   <si>
-    <t>1990000_1840000|1022502_5|1010301_1</t>
+    <t>1990000_41253000|1022502_5|1010301_1</t>
   </si>
   <si>
     <t>1_google799|2_ios799</t>
   </si>
   <si>
-    <t>1990000_2017000|1022502_5|1010301_2</t>
+    <t>1990000_45435000|1022502_5|1010301_2</t>
   </si>
   <si>
     <t>1_google999|2_ios999</t>
   </si>
   <si>
-    <t>1990000_1937000|1022502_10|1010302_2</t>
-  </si>
-  <si>
-    <t>1990000_2537000|1022502_10|1010302_2</t>
+    <t>1990000_41960000|1022502_10|1010302_2</t>
+  </si>
+  <si>
+    <t>1990000_55967000|1022502_10|1010302_2</t>
   </si>
   <si>
     <t>1_google1499|2_ios1499</t>
   </si>
   <si>
-    <t>1990000_2838000|1022502_10|1010302_2</t>
+    <t>1990000_62974000|1022502_10|1010302_2</t>
   </si>
   <si>
     <t>1_google1999|2_ios1999</t>
   </si>
   <si>
-    <t>1990000_3041000|1022502_20|1010303_2</t>
+    <t>1990000_64778000|1022502_20|1010303_2</t>
   </si>
   <si>
     <t>1_google2499|2_ios2499</t>
   </si>
   <si>
-    <t>1990000_4166000|1022502_20|1010303_2</t>
+    <t>1990000_91038000|1022502_20|1010303_2</t>
   </si>
   <si>
     <t>1_google4999|2_ios4999</t>

--- a/slots/resources/sample/PlayerLevelPack.xlsx
+++ b/slots/resources/sample/PlayerLevelPack.xlsx
@@ -109,73 +109,73 @@
     <t>channelCommodity</t>
   </si>
   <si>
-    <t>1990000_297000</t>
+    <t>1990000_1485000</t>
   </si>
   <si>
     <t>1_google99|2_ios99</t>
   </si>
   <si>
-    <t>1990000_597000</t>
+    <t>1990000_2686000</t>
   </si>
   <si>
     <t>1_google199|2_ios199</t>
   </si>
   <si>
-    <t>1990000_567000|1022502_2</t>
-  </si>
-  <si>
-    <t>1990000_867000|1022502_2</t>
+    <t>1990000_2627000|1022502_2</t>
+  </si>
+  <si>
+    <t>1990000_3528000|1022502_2</t>
   </si>
   <si>
     <t>1_googl299|2_ios299</t>
   </si>
   <si>
-    <t>1990000_1317000|1022502_2</t>
+    <t>1990000_5180000|1022502_2</t>
   </si>
   <si>
     <t>1_google499|2_ios499</t>
   </si>
   <si>
-    <t>1990000_1363000|1022502_5</t>
+    <t>1990000_5242000|1022502_5</t>
   </si>
   <si>
     <t>1_google599|2_ios599</t>
   </si>
   <si>
-    <t>1990000_1840000|1022502_5|1010301_1</t>
+    <t>1990000_5841000|1022502_5|1010301_1</t>
   </si>
   <si>
     <t>1_google799|2_ios799</t>
   </si>
   <si>
-    <t>1990000_2017000|1022502_5|1010301_2</t>
+    <t>1990000_5839000|1022502_5|1010301_2</t>
   </si>
   <si>
     <t>1_google999|2_ios999</t>
   </si>
   <si>
-    <t>1990000_1937000|1022502_10|1010302_2</t>
-  </si>
-  <si>
-    <t>1990000_2537000|1022502_10|1010302_2</t>
+    <t>1990000_5685000|1022502_10|1010302_2</t>
+  </si>
+  <si>
+    <t>1990000_7785000|1022502_10|1010302_2</t>
   </si>
   <si>
     <t>1_google1499|2_ios1499</t>
   </si>
   <si>
-    <t>1990000_2838000|1022502_10|1010302_2</t>
+    <t>1990000_8686000|1022502_10|1010302_2</t>
   </si>
   <si>
     <t>1_google1999|2_ios1999</t>
   </si>
   <si>
-    <t>1990000_3041000|1022502_20|1010303_2</t>
+    <t>1990000_8366000|1022502_20|1010303_2</t>
   </si>
   <si>
     <t>1_google2499|2_ios2499</t>
   </si>
   <si>
-    <t>1990000_4166000|1022502_20|1010303_2</t>
+    <t>1990000_12867000|1022502_20|1010303_2</t>
   </si>
   <si>
     <t>1_google4999|2_ios4999</t>

--- a/slots/resources/sample/PlayerLevelPack.xlsx
+++ b/slots/resources/sample/PlayerLevelPack.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="PlayerLevelPack" sheetId="1" r:id="rId1"/>
@@ -109,73 +109,73 @@
     <t>channelCommodity</t>
   </si>
   <si>
-    <t>1990000_6930000</t>
+    <t>1990000_1485000</t>
   </si>
   <si>
     <t>1_google99|2_ios99</t>
   </si>
   <si>
-    <t>1990000_13930000</t>
+    <t>1990000_2686000</t>
   </si>
   <si>
     <t>1_google199|2_ios199</t>
   </si>
   <si>
-    <t>1990000_12544000|1022502_2</t>
-  </si>
-  <si>
-    <t>1990000_19544000|1022502_2</t>
+    <t>1990000_2627000|1022502_2</t>
+  </si>
+  <si>
+    <t>1990000_3528000|1022502_2</t>
   </si>
   <si>
     <t>1_googl299|2_ios299</t>
   </si>
   <si>
-    <t>1990000_30051000|1022502_2</t>
+    <t>1990000_5180000|1022502_2</t>
   </si>
   <si>
     <t>1_google499|2_ios499</t>
   </si>
   <si>
-    <t>1990000_30079000|1022502_5</t>
+    <t>1990000_5242000|1022502_5</t>
   </si>
   <si>
     <t>1_google599|2_ios599</t>
   </si>
   <si>
-    <t>1990000_41253000|1022502_5|1010301_1</t>
+    <t>1990000_5841000|1022502_5|1010301_1</t>
   </si>
   <si>
     <t>1_google799|2_ios799</t>
   </si>
   <si>
-    <t>1990000_45435000|1022502_5|1010301_2</t>
+    <t>1990000_5839000|1022502_5|1010301_2</t>
   </si>
   <si>
     <t>1_google999|2_ios999</t>
   </si>
   <si>
-    <t>1990000_41960000|1022502_10|1010302_2</t>
-  </si>
-  <si>
-    <t>1990000_55967000|1022502_10|1010302_2</t>
+    <t>1990000_5685000|1022502_10|1010302_2</t>
+  </si>
+  <si>
+    <t>1990000_7785000|1022502_10|1010302_2</t>
   </si>
   <si>
     <t>1_google1499|2_ios1499</t>
   </si>
   <si>
-    <t>1990000_62974000|1022502_10|1010302_2</t>
+    <t>1990000_8686000|1022502_10|1010302_2</t>
   </si>
   <si>
     <t>1_google1999|2_ios1999</t>
   </si>
   <si>
-    <t>1990000_64778000|1022502_20|1010303_2</t>
+    <t>1990000_8366000|1022502_20|1010303_2</t>
   </si>
   <si>
     <t>1_google2499|2_ios2499</t>
   </si>
   <si>
-    <t>1990000_91038000|1022502_20|1010303_2</t>
+    <t>1990000_12867000|1022502_20|1010303_2</t>
   </si>
   <si>
     <t>1_google4999|2_ios4999</t>
